--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487206_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487206_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.1658</v>
+        <v>13.7993</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7919</v>
+        <v>8.2113</v>
       </c>
       <c r="F2" t="n">
-        <v>5.3739</v>
+        <v>5.588</v>
       </c>
       <c r="G2" t="n">
         <v>9.6982</v>
@@ -610,13 +610,13 @@
         <v>4.4392</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0066</v>
+        <v>0.627</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0925</v>
+        <v>0.3269</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0859</v>
+        <v>0.3001</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.4364</v>
+        <v>8.3565</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7923</v>
+        <v>5.4714</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6441</v>
+        <v>2.885</v>
       </c>
       <c r="G3" t="n">
         <v>5.4179</v>
@@ -688,13 +688,13 @@
         <v>2.5091</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3602</v>
+        <v>0.5599</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6411</v>
+        <v>0.038</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2809</v>
+        <v>0.5218</v>
       </c>
       <c r="V3" t="n">
         <v>1.7997</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.6284</v>
+        <v>6.7077</v>
       </c>
       <c r="E4" t="n">
-        <v>7.4131</v>
+        <v>7.5727</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7847</v>
+        <v>-0.865</v>
       </c>
       <c r="G4" t="n">
         <v>5.5269</v>
@@ -766,13 +766,13 @@
         <v>0.965</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4224</v>
+        <v>0.5017</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1917</v>
+        <v>0.3513</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2307</v>
+        <v>0.1504</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2859</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.3683</v>
+        <v>4.8607</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2045</v>
+        <v>3.804</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1638</v>
+        <v>1.0567</v>
       </c>
       <c r="G5" t="n">
         <v>3.4851</v>
@@ -844,13 +844,13 @@
         <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1462</v>
+        <v>0.6385</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7998</v>
+        <v>0.3993</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3463</v>
+        <v>0.2393</v>
       </c>
       <c r="V5" t="n">
         <v>-0.614</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4646</v>
+        <v>3.296</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2458</v>
+        <v>1.2646</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2188</v>
+        <v>2.0314</v>
       </c>
       <c r="G6" t="n">
         <v>1.6394</v>
@@ -922,13 +922,13 @@
         <v>2.5091</v>
       </c>
       <c r="S6" t="n">
-        <v>0.544</v>
+        <v>0.3754</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1057</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.4623</v>
       </c>
       <c r="V6" t="n">
         <v>-1.228</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0276</v>
+        <v>3.1942</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2495</v>
+        <v>1.309</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7782</v>
+        <v>1.8853</v>
       </c>
       <c r="G7" t="n">
         <v>2.1406</v>
@@ -1000,13 +1000,13 @@
         <v>2.1231</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.271</v>
+        <v>-0.1044</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1057</v>
+        <v>-0.0462</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1653</v>
+        <v>-0.0582</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.0193</v>
+        <v>2.9717</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3277</v>
+        <v>-0.5092</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3471</v>
+        <v>3.4809</v>
       </c>
       <c r="G8" t="n">
         <v>3.0491</v>
@@ -1078,13 +1078,13 @@
         <v>2.3161</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4158</v>
+        <v>-0.4634</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2247</v>
+        <v>-0.4062</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.191</v>
+        <v>-0.0572</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ALDA IRAOLA</t>
+          <t>U. PEREZ SANZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.6258</v>
+        <v>2.947</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3838</v>
+        <v>0.2232</v>
       </c>
       <c r="F9" t="n">
-        <v>1.242</v>
+        <v>2.7238</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2178</v>
+        <v>2.1098</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4781</v>
+        <v>3.5935</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2602</v>
+        <v>-1.4837</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5251</v>
+        <v>1.3419</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2576</v>
+        <v>3.3533</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7326</v>
+        <v>-2.0114</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3072</v>
+        <v>0.7679</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2204</v>
+        <v>0.2402</v>
       </c>
       <c r="O9" t="n">
         <v>0.5276999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7371</v>
+        <v>2.5091</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1065</v>
+        <v>-0.0929</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6808</v>
+        <v>-0.1537</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4257</v>
+        <v>0.0608</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W9" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. PEREZ SANZ</t>
+          <t>A. ALDA IRAOLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4463</v>
+        <v>2.131</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2775</v>
+        <v>0.9425</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7238</v>
+        <v>1.1885</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1098</v>
+        <v>-0.2178</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5935</v>
+        <v>-1.4781</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4837</v>
+        <v>1.2602</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3419</v>
+        <v>-0.5251</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3533</v>
+        <v>-1.2576</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0114</v>
+        <v>0.7326</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7679</v>
+        <v>0.3072</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2402</v>
+        <v>-0.2204</v>
       </c>
       <c r="O10" t="n">
         <v>0.5276999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5091</v>
+        <v>1.7371</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5936</v>
+        <v>0.6118</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6544</v>
+        <v>0.2396</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0608</v>
+        <v>0.3721</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.614</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0714</v>
+        <v>1.0962</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3489</v>
+        <v>-2.0297</v>
       </c>
       <c r="F11" t="n">
-        <v>3.4203</v>
+        <v>3.1259</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6971000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>2.3161</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1315</v>
+        <v>0.1563</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9518</v>
+        <v>-0.6325</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0833</v>
+        <v>0.7889</v>
       </c>
       <c r="V11" t="n">
         <v>0.2859</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0118</v>
+        <v>-0.2023</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6699</v>
+        <v>1.429</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6581</v>
+        <v>-1.6313</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7504</v>
@@ -1390,13 +1390,13 @@
         <v>1.3511</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5969</v>
+        <v>0.3827</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8593</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2624</v>
+        <v>-0.2357</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1857</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>48.2657</v>
+        <v>49.158</v>
       </c>
       <c r="E13" t="n">
-        <v>26.7967</v>
+        <v>27.6888</v>
       </c>
       <c r="F13" t="n">
         <v>21.4692</v>
       </c>
       <c r="G13" t="n">
-        <v>31.4017</v>
+        <v>31.40170000000001</v>
       </c>
       <c r="H13" t="n">
         <v>13.0871</v>
@@ -1468,10 +1468,10 @@
         <v>24.1261</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3003</v>
+        <v>3.1926</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2443000000000002</v>
+        <v>0.6479999999999999</v>
       </c>
       <c r="U13" t="n">
         <v>2.5446</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.2075</v>
+        <v>-1.8803</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.089</v>
+        <v>0.2115</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.1186</v>
+        <v>-2.0918</v>
       </c>
       <c r="G14" t="n">
         <v>-2.2399</v>
@@ -1546,13 +1546,13 @@
         <v>0.193</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1606</v>
+        <v>0.1666</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1044</v>
+        <v>0.196</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0562</v>
+        <v>-0.0294</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.7984</v>
+        <v>-4.9451</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2102</v>
+        <v>-1.4105</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.5882</v>
+        <v>-3.5346</v>
       </c>
       <c r="G15" t="n">
         <v>-2.9978</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2023</v>
+        <v>-0.349</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4297</v>
+        <v>0.2294</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6319</v>
+        <v>-0.5784</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5983</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.107</v>
+        <v>-6.0396</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.0637</v>
+        <v>-4.264</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0433</v>
+        <v>-1.7756</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3799</v>
@@ -1702,13 +1702,13 @@
         <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.505</v>
+        <v>-0.4376</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0912</v>
+        <v>-0.2915</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4138</v>
+        <v>-0.1461</v>
       </c>
       <c r="V16" t="n">
         <v>3.1122</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>D. MERKVILADZE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-6.8724</v>
+        <v>-6.4436</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.1825</v>
+        <v>0.3962</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6899</v>
+        <v>-6.8398</v>
       </c>
       <c r="G17" t="n">
-        <v>-7.0106</v>
+        <v>-1.8979</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.613</v>
+        <v>-2.0429</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.3977</v>
+        <v>0.1449</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.035</v>
+        <v>3.9004</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.5709</v>
+        <v>0.1811</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4641</v>
+        <v>3.7194</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.9756</v>
+        <v>-5.7983</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.042</v>
+        <v>-2.2239</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.9336</v>
+        <v>-3.5744</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.579</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9453</v>
+        <v>-0.7387</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7827</v>
+        <v>-0.6091</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1626</v>
+        <v>-0.1296</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.228</v>
+        <v>-2.4559</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.228</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. GÓMEZ LÓPEZ</t>
+          <t>M. MENDEZ MADERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-7.0279</v>
+        <v>-6.6609</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8724</v>
+        <v>-4.4002</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.1555</v>
+        <v>-2.2607</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.7163</v>
+        <v>-5.5729</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2805</v>
+        <v>-0.6219</v>
       </c>
       <c r="I18" t="n">
-        <v>-5.4358</v>
+        <v>-4.951</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1926</v>
+        <v>-2.1367</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3557</v>
+        <v>0.3467</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.5483</v>
+        <v>-2.4833</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.5237</v>
+        <v>-3.4362</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6361</v>
+        <v>-0.9685</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.8875</v>
+        <v>-2.4677</v>
       </c>
       <c r="P18" t="n">
+        <v>-1.158</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-1.9301</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-2.8951</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2235</v>
+        <v>0.0701</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6266</v>
+        <v>-0.3334</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5969</v>
+        <v>0.4035</v>
       </c>
       <c r="V18" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MENDEZ MADERA</t>
+          <t>E. GÓMEZ LÓPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-7.0555</v>
+        <v>-6.7473</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.5003</v>
+        <v>-2.6721</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5551</v>
+        <v>-4.0752</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.5729</v>
+        <v>-5.7163</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6219</v>
+        <v>-0.2805</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.951</v>
+        <v>-5.4358</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.1367</v>
+        <v>-1.1926</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3467</v>
+        <v>1.3557</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.4833</v>
+        <v>-2.5483</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.4362</v>
+        <v>-4.5237</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9685</v>
+        <v>-1.6361</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.4677</v>
+        <v>-2.8875</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.158</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R19" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3245</v>
+        <v>-0.9429</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4336</v>
+        <v>-0.4263</v>
       </c>
       <c r="U19" t="n">
-        <v>0.109</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MERKVILADZE</t>
+          <t>C. RIVERA MOTA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.0652</v>
+        <v>-7.1735</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0958</v>
+        <v>-3.0461</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.161</v>
+        <v>-4.1274</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8979</v>
+        <v>-4.5864</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0429</v>
+        <v>-2.1559</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1449</v>
+        <v>-2.4305</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9004</v>
+        <v>0.051</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1811</v>
+        <v>-0.0054</v>
       </c>
       <c r="L20" t="n">
-        <v>3.7194</v>
+        <v>0.0564</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.7983</v>
+        <v>-4.6374</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2239</v>
+        <v>-2.1504</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.5744</v>
+        <v>-2.487</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3511</v>
+        <v>-4.2462</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.8951</v>
+        <v>-5.7902</v>
       </c>
       <c r="R20" t="n">
         <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3603</v>
+        <v>-0.511</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9095</v>
+        <v>-0.9908</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4508</v>
+        <v>0.4798</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4559</v>
+        <v>2.1701</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.6839</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4559</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. RIVERA MOTA</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.1319</v>
+        <v>-8.375400000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.647</v>
+        <v>-6.284</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4849</v>
+        <v>-2.0914</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.5864</v>
+        <v>-7.0106</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1559</v>
+        <v>-4.613</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4305</v>
+        <v>-2.3977</v>
       </c>
       <c r="J21" t="n">
-        <v>0.051</v>
+        <v>-4.035</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0054</v>
+        <v>-3.5709</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0564</v>
+        <v>-0.4641</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.6374</v>
+        <v>-2.9756</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.1504</v>
+        <v>-1.042</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.487</v>
+        <v>-1.9336</v>
       </c>
       <c r="P21" t="n">
-        <v>-4.2462</v>
+        <v>-0.579</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.7902</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4693</v>
+        <v>0.4422</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5916</v>
+        <v>-0.3189</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1223</v>
+        <v>0.7611</v>
       </c>
       <c r="V21" t="n">
-        <v>2.1701</v>
+        <v>-1.228</v>
       </c>
       <c r="W21" t="n">
-        <v>3.6839</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5138</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-48.2658</v>
+        <v>-48.2657</v>
       </c>
       <c r="E22" t="n">
-        <v>-21.4693</v>
+        <v>-21.4692</v>
       </c>
       <c r="F22" t="n">
-        <v>-26.79649999999999</v>
+        <v>-26.7965</v>
       </c>
       <c r="G22" t="n">
         <v>-31.4017</v>
@@ -2149,7 +2149,7 @@
         <v>-1.9673</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4424999999999994</v>
+        <v>-0.442499999999999</v>
       </c>
       <c r="M22" t="n">
         <v>-28.9917</v>
@@ -2167,16 +2167,16 @@
         <v>-24.126</v>
       </c>
       <c r="R22" t="n">
-        <v>7.720400000000001</v>
+        <v>7.7204</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3002</v>
+        <v>-2.3003</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.5445</v>
+        <v>-2.5446</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2443000000000002</v>
+        <v>0.2443</v>
       </c>
       <c r="V22" t="n">
         <v>1.8421</v>
